--- a/datasets/day1_excel_foundations/homework/d1_homework_start.xlsx
+++ b/datasets/day1_excel_foundations/homework/d1_homework_start.xlsx
@@ -503,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -539,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1799</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1259</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -647,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>3980</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="8">
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1003</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>794</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +791,7 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>6777.6</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="11">
@@ -827,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2898</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>165.3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2759.4</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="16">
@@ -1007,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1050</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
@@ -1043,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -1079,7 +1079,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1928</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19">
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20">
@@ -1151,7 +1151,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>212</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1581</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="22">
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1433</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1737</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>812</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25">
@@ -1331,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1244</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26">
@@ -1367,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>312</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27">
@@ -1403,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>2561.4</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="28">
@@ -1439,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>645</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29">
@@ -1475,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>548.25</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30">
@@ -1511,7 +1511,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>43.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -1547,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32">
@@ -1583,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1996</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="33">
@@ -1619,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1608.35</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="34">
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>848</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35">
@@ -1691,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
